--- a/output/StructureDefinition-BRObservacaoDescritiva-1.0.xlsx
+++ b/output/StructureDefinition-BRObservacaoDescritiva-1.0.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="594">
   <si>
     <t>Property</t>
   </si>
@@ -1629,6 +1629,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -9444,7 +9448,7 @@
         <v>516</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>517</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>83</v>
@@ -9453,10 +9457,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9467,10 +9471,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9496,10 +9500,10 @@
         <v>513</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9550,7 +9554,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9562,7 +9566,7 @@
         <v>516</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>517</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>83</v>
@@ -9571,10 +9575,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9585,10 +9589,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9614,16 +9618,16 @@
         <v>190</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9651,10 +9655,10 @@
         <v>117</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9672,7 +9676,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9690,10 +9694,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>448</v>
@@ -9707,10 +9711,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9736,16 +9740,16 @@
         <v>190</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9773,10 +9777,10 @@
         <v>462</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9794,7 +9798,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9812,10 +9816,10 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>448</v>
@@ -9829,10 +9833,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9855,17 +9859,17 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9914,7 +9918,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9938,7 +9942,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9949,10 +9953,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9978,10 +9982,10 @@
         <v>215</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10032,7 +10036,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10053,10 +10057,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10067,10 +10071,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10093,16 +10097,16 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10152,7 +10156,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10173,10 +10177,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10187,10 +10191,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10213,16 +10217,16 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10272,7 +10276,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10293,10 +10297,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10307,10 +10311,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10336,16 +10340,16 @@
         <v>497</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10394,7 +10398,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10415,10 +10419,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10429,10 +10433,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10547,10 +10551,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10667,10 +10671,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10789,10 +10793,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10818,13 +10822,13 @@
         <v>190</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>204</v>
@@ -10855,10 +10859,10 @@
         <v>462</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10876,7 +10880,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>94</v>
@@ -10894,7 +10898,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>210</v>
@@ -10911,10 +10915,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10937,16 +10941,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>423</v>
@@ -10998,7 +11002,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11016,7 +11020,7 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>426</v>
@@ -11033,10 +11037,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11062,13 +11066,13 @@
         <v>190</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>433</v>
@@ -11120,7 +11124,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11155,10 +11159,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11242,7 +11246,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11277,10 +11281,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11306,10 +11310,10 @@
         <v>83</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>500</v>
@@ -11364,7 +11368,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
